--- a/samples/수출신고내역_2026.xlsx
+++ b/samples/수출신고내역_2026.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:K19"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -430,6 +430,9 @@
       <c r="J1" t="str">
         <v>도착국</v>
       </c>
+      <c r="K1" t="str">
+        <v>HS부호</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -910,10 +913,118 @@
       <c r="J16" t="str">
         <v>멕시코</v>
       </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>41234-26-0100161X</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-05-10</v>
+      </c>
+      <c r="C17" t="str">
+        <v>CNC Milling Machine</v>
+      </c>
+      <c r="D17" t="str">
+        <v>VMC-850</v>
+      </c>
+      <c r="E17" t="str">
+        <v>4200</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17" t="str">
+        <v>USD</v>
+      </c>
+      <c r="H17">
+        <v>85000</v>
+      </c>
+      <c r="I17" t="str">
+        <v>FOB</v>
+      </c>
+      <c r="J17" t="str">
+        <v>인도네시아</v>
+      </c>
+      <c r="K17" t="str">
+        <v>8459.61-0000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>41234-26-0100172X</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="C18" t="str">
+        <v>AI Server</v>
+      </c>
+      <c r="D18" t="str">
+        <v>SVR-H100-8U</v>
+      </c>
+      <c r="E18" t="str">
+        <v>120</v>
+      </c>
+      <c r="F18">
+        <v>2</v>
+      </c>
+      <c r="G18" t="str">
+        <v>USD</v>
+      </c>
+      <c r="H18">
+        <v>520000</v>
+      </c>
+      <c r="I18" t="str">
+        <v>FOB</v>
+      </c>
+      <c r="J18" t="str">
+        <v>싱가포르</v>
+      </c>
+      <c r="K18" t="str">
+        <v>8471.49-9000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>41234-26-0100183X</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2026-05-20</v>
+      </c>
+      <c r="C19" t="str">
+        <v>RF Module Assembly</v>
+      </c>
+      <c r="D19" t="str">
+        <v>SLS-4400B</v>
+      </c>
+      <c r="E19" t="str">
+        <v>18</v>
+      </c>
+      <c r="F19">
+        <v>6</v>
+      </c>
+      <c r="G19" t="str">
+        <v>EUR</v>
+      </c>
+      <c r="H19">
+        <v>54000</v>
+      </c>
+      <c r="I19" t="str">
+        <v>CIF</v>
+      </c>
+      <c r="J19" t="str">
+        <v>폴란드</v>
+      </c>
+      <c r="K19" t="str">
+        <v>8517.79-2000</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K19"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/samples/수출신고내역_2026.xlsx
+++ b/samples/수출신고내역_2026.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K20"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1022,9 +1022,44 @@
         <v>8517.79-2000</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>41234-26-0100194X</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2026-05-25</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Telecom Transmission Module</v>
+      </c>
+      <c r="D20" t="str">
+        <v>TTM-300</v>
+      </c>
+      <c r="E20" t="str">
+        <v>9</v>
+      </c>
+      <c r="F20">
+        <v>12</v>
+      </c>
+      <c r="G20" t="str">
+        <v>USD</v>
+      </c>
+      <c r="H20">
+        <v>36000</v>
+      </c>
+      <c r="I20" t="str">
+        <v>FOB</v>
+      </c>
+      <c r="J20" t="str">
+        <v>브라질</v>
+      </c>
+      <c r="K20" t="str">
+        <v>8517.62-1000</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K20"/>
   </ignoredErrors>
 </worksheet>
 </file>